--- a/Games/Booklets/Everspace 2/maps/00_Pointers/Coordinates.xlsx
+++ b/Games/Booklets/Everspace 2/maps/00_Pointers/Coordinates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.bey\Documents\GitHub\homepage\Games\Booklets\Everspace 2\maps\00_Pointers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D022CD8-738F-40FE-BAFB-01DAC30DAD90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BF83EC4-3A95-4E1A-8B52-21143999A498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3093,7 +3093,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2625B6A-8B67-4431-A6B4-850D2B09C94D}">
-  <dimension ref="A1:V410"/>
+  <dimension ref="A1:V411"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1" customWidth="1"/>
@@ -9904,7 +9904,7 @@
       <c r="T240" s="6"/>
     </row>
     <row r="241" spans="1:20" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:20" ht="5.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="6"/>
       <c r="B242" s="6"/>
       <c r="C242" s="6"/>
@@ -10199,7 +10199,7 @@
       <c r="S251" s="10"/>
       <c r="T251" s="6"/>
     </row>
-    <row r="252" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:20" ht="5.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="7"/>
       <c r="B252" s="6"/>
       <c r="C252" s="6"/>
@@ -10221,7 +10221,7 @@
       <c r="S252" s="6"/>
       <c r="T252" s="6"/>
     </row>
-    <row r="253" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:20" ht="5.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="6"/>
       <c r="B253" s="6"/>
       <c r="C253" s="6"/>
@@ -10516,7 +10516,7 @@
       <c r="S262" s="10"/>
       <c r="T262" s="6"/>
     </row>
-    <row r="263" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:20" ht="5.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="7"/>
       <c r="B263" s="6"/>
       <c r="C263" s="6"/>
@@ -10538,7 +10538,7 @@
       <c r="S263" s="6"/>
       <c r="T263" s="6"/>
     </row>
-    <row r="264" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:20" ht="5.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="6"/>
       <c r="B264" s="6"/>
       <c r="C264" s="6"/>
@@ -10833,7 +10833,7 @@
       <c r="S273" s="10"/>
       <c r="T273" s="6"/>
     </row>
-    <row r="274" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:20" ht="5.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="7"/>
       <c r="B274" s="6"/>
       <c r="C274" s="6"/>
@@ -10855,7 +10855,8 @@
       <c r="S274" s="6"/>
       <c r="T274" s="6"/>
     </row>
-    <row r="276" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:20" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" spans="1:20" ht="5.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="6"/>
       <c r="B276" s="6"/>
       <c r="C276" s="6"/>
@@ -11150,7 +11151,7 @@
       <c r="S285" s="10"/>
       <c r="T285" s="6"/>
     </row>
-    <row r="286" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:20" ht="5.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="7"/>
       <c r="B286" s="6"/>
       <c r="C286" s="6"/>
@@ -11172,7 +11173,7 @@
       <c r="S286" s="6"/>
       <c r="T286" s="6"/>
     </row>
-    <row r="287" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:20" ht="5.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="6"/>
       <c r="B287" s="6"/>
       <c r="C287" s="6"/>
@@ -11467,7 +11468,7 @@
       <c r="S296" s="10"/>
       <c r="T296" s="6"/>
     </row>
-    <row r="297" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:20" ht="5.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="7"/>
       <c r="B297" s="6"/>
       <c r="C297" s="6"/>
@@ -11489,7 +11490,7 @@
       <c r="S297" s="6"/>
       <c r="T297" s="6"/>
     </row>
-    <row r="298" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:20" ht="5.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="6"/>
       <c r="B298" s="6"/>
       <c r="C298" s="6"/>
@@ -11782,7 +11783,7 @@
       <c r="S307" s="10"/>
       <c r="T307" s="6"/>
     </row>
-    <row r="308" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:20" ht="5.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="7"/>
       <c r="B308" s="6"/>
       <c r="C308" s="6"/>
@@ -11804,7 +11805,8 @@
       <c r="S308" s="6"/>
       <c r="T308" s="6"/>
     </row>
-    <row r="310" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:20" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" spans="1:20" ht="5.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="6"/>
       <c r="B310" s="6"/>
       <c r="C310" s="6"/>
@@ -12097,7 +12099,7 @@
       <c r="S319" s="10"/>
       <c r="T319" s="6"/>
     </row>
-    <row r="320" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:20" ht="5.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="7"/>
       <c r="B320" s="6"/>
       <c r="C320" s="6"/>
@@ -12119,7 +12121,7 @@
       <c r="S320" s="6"/>
       <c r="T320" s="6"/>
     </row>
-    <row r="321" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:20" ht="5.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="6"/>
       <c r="B321" s="6"/>
       <c r="C321" s="6"/>
@@ -12412,7 +12414,7 @@
       <c r="S330" s="10"/>
       <c r="T330" s="6"/>
     </row>
-    <row r="331" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:20" ht="5.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="7"/>
       <c r="B331" s="6"/>
       <c r="C331" s="6"/>
@@ -12434,7 +12436,7 @@
       <c r="S331" s="6"/>
       <c r="T331" s="6"/>
     </row>
-    <row r="332" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:20" ht="5.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="6"/>
       <c r="B332" s="6"/>
       <c r="C332" s="6"/>
@@ -12727,7 +12729,7 @@
       <c r="S341" s="10"/>
       <c r="T341" s="6"/>
     </row>
-    <row r="342" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:20" ht="5.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="7"/>
       <c r="B342" s="6"/>
       <c r="C342" s="6"/>
@@ -12749,7 +12751,8 @@
       <c r="S342" s="6"/>
       <c r="T342" s="6"/>
     </row>
-    <row r="344" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:20" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" spans="1:20" ht="5.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="6"/>
       <c r="B344" s="6"/>
       <c r="C344" s="6"/>
@@ -13042,7 +13045,7 @@
       <c r="S353" s="10"/>
       <c r="T353" s="6"/>
     </row>
-    <row r="354" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:20" ht="5.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="7"/>
       <c r="B354" s="6"/>
       <c r="C354" s="6"/>
@@ -13064,7 +13067,7 @@
       <c r="S354" s="6"/>
       <c r="T354" s="6"/>
     </row>
-    <row r="355" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:20" ht="5.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="6"/>
       <c r="B355" s="6"/>
       <c r="C355" s="6"/>
@@ -13357,7 +13360,7 @@
       <c r="S364" s="10"/>
       <c r="T364" s="6"/>
     </row>
-    <row r="365" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:20" ht="5.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="7"/>
       <c r="B365" s="6"/>
       <c r="C365" s="6"/>
@@ -13379,7 +13382,7 @@
       <c r="S365" s="6"/>
       <c r="T365" s="6"/>
     </row>
-    <row r="366" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:20" ht="5.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="6"/>
       <c r="B366" s="6"/>
       <c r="C366" s="6"/>
@@ -13672,7 +13675,7 @@
       <c r="S375" s="10"/>
       <c r="T375" s="6"/>
     </row>
-    <row r="376" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:20" ht="5.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="7"/>
       <c r="B376" s="6"/>
       <c r="C376" s="6"/>
@@ -13694,7 +13697,8 @@
       <c r="S376" s="6"/>
       <c r="T376" s="6"/>
     </row>
-    <row r="378" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:20" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" spans="1:20" ht="5.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="6"/>
       <c r="B378" s="6"/>
       <c r="C378" s="6"/>
@@ -13987,7 +13991,7 @@
       <c r="S387" s="10"/>
       <c r="T387" s="6"/>
     </row>
-    <row r="388" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:20" ht="5.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="7"/>
       <c r="B388" s="6"/>
       <c r="C388" s="6"/>
@@ -14009,7 +14013,7 @@
       <c r="S388" s="6"/>
       <c r="T388" s="6"/>
     </row>
-    <row r="389" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:20" ht="5.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="6"/>
       <c r="B389" s="6"/>
       <c r="C389" s="6"/>
@@ -14302,7 +14306,7 @@
       <c r="S398" s="10"/>
       <c r="T398" s="6"/>
     </row>
-    <row r="399" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:20" ht="5.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="7"/>
       <c r="B399" s="6"/>
       <c r="C399" s="6"/>
@@ -14324,7 +14328,7 @@
       <c r="S399" s="6"/>
       <c r="T399" s="6"/>
     </row>
-    <row r="400" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:20" ht="5.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="6"/>
       <c r="B400" s="6"/>
       <c r="C400" s="6"/>
@@ -14617,7 +14621,7 @@
       <c r="S409" s="10"/>
       <c r="T409" s="6"/>
     </row>
-    <row r="410" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:20" ht="5.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="7"/>
       <c r="B410" s="6"/>
       <c r="C410" s="6"/>
@@ -14639,6 +14643,7 @@
       <c r="S410" s="6"/>
       <c r="T410" s="6"/>
     </row>
+    <row r="411" spans="1:20" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="722">
     <mergeCell ref="H5:H11"/>
